--- a/static/data/exports/Retro_PB_AE_2022.xlsx
+++ b/static/data/exports/Retro_PB_AE_2022.xlsx
@@ -16696,20 +16696,20 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>1733116</v>
+        <v>1733117</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Gurpreet Singh</t>
+          <t>Gopi Singh</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>APNJBP</t>
+          <t>NATJUP</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>22355</v>
+        <v>22327</v>
       </c>
       <c r="E221" t="n">
         <v>169</v>
@@ -16733,12 +16733,12 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>Gurpreet Singh</t>
+          <t>Gopi Singh</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>APNJBP</t>
+          <t>NATJUP</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -16752,7 +16752,7 @@
         </is>
       </c>
       <c r="P221" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q221" t="b">
         <v>0</v>
@@ -16771,20 +16771,20 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>1733117</v>
+        <v>1733116</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Gopi Singh</t>
+          <t>Gurpreet Singh</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>NATJUP</t>
+          <t>APNJBP</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>22327</v>
+        <v>22355</v>
       </c>
       <c r="E222" t="n">
         <v>169</v>
@@ -16808,12 +16808,12 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Gopi Singh</t>
+          <t>Gurpreet Singh</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>NATJUP</t>
+          <t>APNJBP</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16827,7 +16827,7 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q222" t="b">
         <v>0</v>
@@ -84417,11 +84417,11 @@
       </c>
       <c r="C1137" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1137" t="n">
-        <v>22461</v>
+        <v>22339</v>
       </c>
       <c r="E1137" t="n">
         <v>639</v>
